--- a/data/trans_dic/IP12B$alergia-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,92</t>
+          <t>0,0; 28,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,99</t>
+          <t>0,0; 44,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,15</t>
+          <t>0,0; 28,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 12,57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,63</t>
+          <t>0,0; 31,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,08</t>
+          <t>0,0; 23,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,34</t>
+          <t>0,0; 39,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,81</t>
+          <t>0,0; 52,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,34</t>
+          <t>0,0; 22,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,69</t>
+          <t>0,0; 27,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,09</t>
+          <t>0,0; 15,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,1</t>
+          <t>0,0; 26,82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,16</t>
+          <t>0,0; 57,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,91</t>
+          <t>0,0; 30,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,25</t>
+          <t>0,0; 55,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,0</t>
+          <t>0,0; 41,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,37</t>
+          <t>0,0; 32,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,13</t>
+          <t>0,0; 61,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,93</t>
+          <t>0,0; 28,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,71</t>
+          <t>0,0; 34,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,48</t>
+          <t>0,0; 22,4</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,01</t>
+          <t>0,0; 55,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,52</t>
+          <t>0,0; 28,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,79</t>
+          <t>0,0; 79,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,7</t>
+          <t>0,0; 41,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,2</t>
+          <t>0,0; 50,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,73</t>
+          <t>0,0; 63,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,69</t>
+          <t>0,0; 46,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,03</t>
+          <t>0,0; 55,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,01</t>
+          <t>0,0; 30,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,74</t>
+          <t>0,0; 25,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,85</t>
+          <t>0,0; 43,45</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,08; 45,43</t>
+          <t>6,05; 44,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,54; 20,2</t>
+          <t>2,59; 21,57</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,21</t>
+          <t>1,45; 12,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 8,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,37; 15,18</t>
+          <t>2,37; 14,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 12,06</t>
+          <t>1,27; 10,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,95</t>
+          <t>2,35; 14,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,14</t>
+          <t>1,4; 12,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,9</t>
+          <t>1,59; 8,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,4</t>
+          <t>2,03; 9,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 11,19</t>
+          <t>2,82; 11,34</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2642</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3621</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3699</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2427</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3292</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2820</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3655</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3039</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3133</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4389</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4042</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4619</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4181</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4725</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3611</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4064</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2618</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3885</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4156</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5071</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4373</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4689</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4205</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2919</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2815</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3007</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2587</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2827</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2700</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3552</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3353</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4692</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>622; 4601</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>617; 5142</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5757</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>6230</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>637; 5594</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0; 5009</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1306; 7851</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>592; 5107</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1492; 9129</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>669; 6180</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1438; 8142</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2532; 11980</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2904; 11675</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$alergia-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,82</t>
+          <t>0,0; 31,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,01</t>
+          <t>0,0; 49,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,08</t>
+          <t>0,0; 34,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,57</t>
+          <t>0,0; 15,34</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,94</t>
+          <t>0,0; 30,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,23</t>
+          <t>0,0; 28,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,67</t>
+          <t>0,0; 40,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,22</t>
+          <t>0,0; 50,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,53</t>
+          <t>0,0; 19,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,21</t>
+          <t>0,0; 25,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,52</t>
+          <t>0,0; 15,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,82</t>
+          <t>0,0; 22,26</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,43</t>
+          <t>0,0; 48,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,88</t>
+          <t>0,0; 35,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,98</t>
+          <t>0,0; 47,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,3</t>
+          <t>0,0; 41,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,03</t>
+          <t>0,0; 38,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,15</t>
+          <t>0,0; 66,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,42</t>
+          <t>0,0; 33,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,06</t>
+          <t>0,0; 34,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,4</t>
+          <t>0,0; 22,26</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,89</t>
+          <t>0,0; 44,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,49</t>
+          <t>0,0; 25,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,75</t>
+          <t>0,0; 42,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,54</t>
+          <t>0,0; 59,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,8</t>
+          <t>0,0; 48,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,7</t>
+          <t>0,0; 56,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,58</t>
+          <t>0,0; 32,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,41</t>
+          <t>0,0; 20,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,45</t>
+          <t>0,0; 38,12</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 44,76</t>
+          <t>6,11; 43,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 21,57</t>
+          <t>2,62; 22,21</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,75</t>
+          <t>1,45; 13,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,17</t>
+          <t>0,0; 8,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,37; 14,24</t>
+          <t>1,82; 13,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,93</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,36</t>
+          <t>2,46; 15,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,91</t>
+          <t>1,37; 13,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,99</t>
+          <t>1,99; 9,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,59</t>
+          <t>1,84; 9,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,34</t>
+          <t>2,9; 11,42</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2642</t>
+          <t>0; 2900</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3621</t>
+          <t>0; 4074</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3699</t>
+          <t>0; 4490</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2427</t>
+          <t>0; 2961</t>
         </is>
       </c>
     </row>
@@ -2024,27 +2024,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3292</t>
+          <t>0; 3134</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2820</t>
+          <t>0; 3503</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3655</t>
+          <t>0; 3706</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3039</t>
+          <t>0; 2917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3133</t>
+          <t>0; 2774</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4389</t>
+          <t>0; 4039</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4042</t>
+          <t>0; 4064</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4619</t>
+          <t>0; 3834</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4181</t>
+          <t>0; 3566</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4725</t>
+          <t>0; 5371</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3611</t>
+          <t>0; 3059</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4064</t>
+          <t>0; 4130</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2618</t>
+          <t>0; 3162</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3885</t>
+          <t>0; 4229</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4156</t>
+          <t>0; 4896</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5071</t>
+          <t>0; 5161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4373</t>
+          <t>0; 4345</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4689</t>
+          <t>0; 3696</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4205</t>
+          <t>0; 3733</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2815</t>
+          <t>0; 2890</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3007</t>
+          <t>0; 3530</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2859,27 +2859,27 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2827</t>
+          <t>0; 2906</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2700</t>
+          <t>0; 2754</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3552</t>
+          <t>0; 3718</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3353</t>
+          <t>0; 2676</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4692</t>
+          <t>0; 4117</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>622; 4601</t>
+          <t>628; 4519</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>617; 5142</t>
+          <t>626; 5295</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>637; 5594</t>
+          <t>635; 5891</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 5009</t>
+          <t>0; 5198</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1306; 7851</t>
+          <t>1004; 7595</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>592; 5107</t>
+          <t>0; 4541</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1492; 9129</t>
+          <t>1560; 9698</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>669; 6180</t>
+          <t>657; 6443</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1438; 8142</t>
+          <t>1798; 8169</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2532; 11980</t>
+          <t>2299; 11711</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2904; 11675</t>
+          <t>2982; 11763</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$alergia-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>5,48%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 44,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,09</t>
+          <t>0,0; 41,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,34</t>
+          <t>0,0; 14,97</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,13%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,72%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,69%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,4</t>
+          <t>0,0; 46,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,86</t>
+          <t>0,0; 22,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,12</t>
+          <t>0,0; 30,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,95</t>
+          <t>0,0; 23,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,04</t>
+          <t>0,0; 23,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,61</t>
+          <t>0,0; 17,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,26</t>
+          <t>0,0; 22,1</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 49,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,1</t>
+          <t>0,0; 24,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>12,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,81%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,43</t>
+          <t>0,0; 38,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 64,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,69</t>
+          <t>0,0; 49,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 43,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,48</t>
+          <t>0,0; 27,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,67</t>
+          <t>0,0; 37,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,26</t>
+          <t>0,0; 22,48</t>
         </is>
       </c>
     </row>
@@ -1070,22 +1070,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>10,43%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,29</t>
+          <t>0,0; 24,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>19,02%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 79,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,85</t>
+          <t>0,0; 42,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>13,46%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>12,97%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 65,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 48,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,32</t>
+          <t>0,0; 63,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,81</t>
+          <t>0,0; 50,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,01</t>
+          <t>0,0; 37,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,28</t>
+          <t>0,0; 24,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,12</t>
+          <t>0,0; 40,85</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,08; 45,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,11; 43,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 22,21</t>
+          <t>2,54; 20,2</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,83%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6,56%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,43</t>
+          <t>1,25; 12,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,48</t>
+          <t>2,62; 14,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 13,78</t>
+          <t>1,38; 13,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>1,45; 13,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,26</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 13,46</t>
+          <t>2,37; 15,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,02</t>
+          <t>1,57; 8,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,84; 9,38</t>
+          <t>2,06; 9,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,42</t>
+          <t>2,88; 11,19</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1760,27 +1760,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1813,27 +1813,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>900</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>502</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3702</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2900</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2743</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4490</t>
+          <t>0; 5420</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2961</t>
+          <t>0; 2891</t>
         </is>
       </c>
     </row>
@@ -1928,22 +1928,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>985</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3134</t>
+          <t>0; 2724</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3503</t>
+          <t>0; 3107</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2917</t>
+          <t>0; 3157</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2774</t>
+          <t>0; 2801</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3809</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4039</t>
+          <t>0; 3820</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4064</t>
+          <t>0; 4451</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3834</t>
+          <t>0; 3805</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>984</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3579</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3566</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5371</t>
+          <t>0; 3811</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2249,27 +2249,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1359</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1052</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3059</t>
+          <t>0; 3135</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4130</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3162</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4232</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4896</t>
+          <t>0; 4084</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5161</t>
+          <t>0; 5614</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4345</t>
+          <t>0; 4388</t>
         </is>
       </c>
     </row>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2465,22 +2465,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>875</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3696</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4615</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3733</t>
+          <t>0; 3619</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2623,22 +2623,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>696</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2919</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2890</t>
+          <t>0; 2880</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>624</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>772</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2658</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2941</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3530</t>
+          <t>0; 3055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2587</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2754</t>
+          <t>0; 2988</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3718</t>
+          <t>0; 4299</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2676</t>
+          <t>0; 3265</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4117</t>
+          <t>0; 4411</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>625; 4670</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>628; 4519</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>626; 5295</t>
+          <t>605; 4815</t>
         </is>
       </c>
     </row>
@@ -3064,27 +3064,27 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>2120</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1570</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>3618</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>4187</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>635; 5891</t>
+          <t>586; 5633</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 5198</t>
+          <t>1668; 9499</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1004; 7595</t>
+          <t>659; 6287</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0; 4541</t>
+          <t>634; 5796</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1560; 9698</t>
+          <t>0; 4880</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>657; 6443</t>
+          <t>1305; 8368</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1798; 8169</t>
+          <t>1425; 8063</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2299; 11711</t>
+          <t>2571; 11735</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2982; 11763</t>
+          <t>2964; 11520</t>
         </is>
       </c>
     </row>
